--- a/gcam/output/SSP2/iamc_template_gcam_other.xlsx
+++ b/gcam/output/SSP2/iamc_template_gcam_other.xlsx
@@ -223,7 +223,7 @@
     <t>degC</t>
   </si>
   <si>
-    <t>MtC/yr</t>
+    <t>MtCO2/yr</t>
   </si>
 </sst>
 </file>
@@ -6245,70 +6245,70 @@
         <v>69</v>
       </c>
       <c r="F69">
-        <v>2.685467169</v>
+        <v>9.846712952999999</v>
       </c>
       <c r="G69">
-        <v>6.887464960700001</v>
+        <v>25.25403818923334</v>
       </c>
       <c r="H69">
-        <v>12.0500971124</v>
+        <v>44.18368941213334</v>
       </c>
       <c r="I69">
-        <v>17.38970952133</v>
+        <v>63.76226824487666</v>
       </c>
       <c r="J69">
-        <v>21.575193945352</v>
+        <v>79.10904446629067</v>
       </c>
       <c r="K69">
-        <v>25.175611518137</v>
+        <v>92.31057556650234</v>
       </c>
       <c r="L69">
-        <v>29.6799011937504</v>
+        <v>108.8263043770848</v>
       </c>
       <c r="M69">
-        <v>35.25415651185492</v>
+        <v>129.2652405434681</v>
       </c>
       <c r="N69">
-        <v>43.33268921254802</v>
+        <v>158.8865271126761</v>
       </c>
       <c r="O69">
-        <v>30.47269563783445</v>
+        <v>111.7332173387263</v>
       </c>
       <c r="P69">
-        <v>13.79754081232854</v>
+        <v>50.59098297853799</v>
       </c>
       <c r="Q69">
-        <v>2.041708732643872</v>
+        <v>7.486265353027531</v>
       </c>
       <c r="R69">
-        <v>-5.925266621156727</v>
+        <v>-21.725977610908</v>
       </c>
       <c r="S69">
-        <v>-7.947540323759798</v>
+        <v>-29.14098118711926</v>
       </c>
       <c r="T69">
-        <v>-6.990123235860637</v>
+        <v>-25.63045186482234</v>
       </c>
       <c r="U69">
-        <v>-4.839004425530838</v>
+        <v>-17.74301622694641</v>
       </c>
       <c r="V69">
-        <v>-4.661874492421879</v>
+        <v>-17.09353980554689</v>
       </c>
       <c r="W69">
-        <v>-4.097005026597143</v>
+        <v>-15.02235176418952</v>
       </c>
       <c r="X69">
-        <v>-4.429309910501796</v>
+        <v>-16.24080300517325</v>
       </c>
       <c r="Y69">
-        <v>-4.994005034478003</v>
+        <v>-18.31135179308601</v>
       </c>
       <c r="Z69">
-        <v>-6.011536890919284</v>
+        <v>-22.04230193337071</v>
       </c>
       <c r="AA69">
-        <v>2.717508635729339</v>
+        <v>9.964198331007577</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -6328,70 +6328,70 @@
         <v>69</v>
       </c>
       <c r="F70">
-        <v>19.414345079</v>
+        <v>71.18593195633333</v>
       </c>
       <c r="G70">
-        <v>67.418306415765</v>
+        <v>247.200456857805</v>
       </c>
       <c r="H70">
-        <v>112.17997964207</v>
+        <v>411.3265920209233</v>
       </c>
       <c r="I70">
-        <v>133.758375228078</v>
+        <v>490.447375836286</v>
       </c>
       <c r="J70">
-        <v>153.94569403639</v>
+        <v>564.4675448000967</v>
       </c>
       <c r="K70">
-        <v>169.61551508994</v>
+        <v>621.92355532978</v>
       </c>
       <c r="L70">
-        <v>185.70838925279</v>
+        <v>680.9307605935634</v>
       </c>
       <c r="M70">
-        <v>201.487504915285</v>
+        <v>738.7875180227117</v>
       </c>
       <c r="N70">
-        <v>223.669211484696</v>
+        <v>820.1204421105521</v>
       </c>
       <c r="O70">
-        <v>160.4260148986938</v>
+        <v>588.2287212952107</v>
       </c>
       <c r="P70">
-        <v>122.7626988232123</v>
+        <v>450.1298956851116</v>
       </c>
       <c r="Q70">
-        <v>98.99300586475354</v>
+        <v>362.9743548374296</v>
       </c>
       <c r="R70">
-        <v>90.95656537486104</v>
+        <v>333.5074063744905</v>
       </c>
       <c r="S70">
-        <v>88.03105067199529</v>
+        <v>322.7805191306494</v>
       </c>
       <c r="T70">
-        <v>84.80332044181259</v>
+        <v>310.9455082866461</v>
       </c>
       <c r="U70">
-        <v>80.3948413199254</v>
+        <v>294.7810848397265</v>
       </c>
       <c r="V70">
-        <v>73.92235401362537</v>
+        <v>271.048631383293</v>
       </c>
       <c r="W70">
-        <v>66.01053741786473</v>
+        <v>242.0386371988373</v>
       </c>
       <c r="X70">
-        <v>58.3929079179662</v>
+        <v>214.1073290325427</v>
       </c>
       <c r="Y70">
-        <v>46.66676791626917</v>
+        <v>171.1114823596536</v>
       </c>
       <c r="Z70">
-        <v>36.66123396035743</v>
+        <v>134.4245245213106</v>
       </c>
       <c r="AA70">
-        <v>28.7743615725999</v>
+        <v>105.5059924328663</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -6411,70 +6411,70 @@
         <v>69</v>
       </c>
       <c r="F71">
-        <v>4.613721474</v>
+        <v>16.916978738</v>
       </c>
       <c r="G71">
-        <v>12.4200417986</v>
+        <v>45.54015326153333</v>
       </c>
       <c r="H71">
-        <v>13.9510607976</v>
+        <v>51.1538895912</v>
       </c>
       <c r="I71">
-        <v>16.300991368</v>
+        <v>59.77030168266668</v>
       </c>
       <c r="J71">
-        <v>23.56070651995</v>
+        <v>86.38925723981667</v>
       </c>
       <c r="K71">
-        <v>23.4619035927</v>
+        <v>86.02697983989999</v>
       </c>
       <c r="L71">
-        <v>28.90998029979</v>
+        <v>106.00326109923</v>
       </c>
       <c r="M71">
-        <v>36.24443325298654</v>
+        <v>132.8962552609507</v>
       </c>
       <c r="N71">
-        <v>45.71386234336008</v>
+        <v>167.617495258987</v>
       </c>
       <c r="O71">
-        <v>29.57968944975158</v>
+        <v>108.4588613157558</v>
       </c>
       <c r="P71">
-        <v>17.12456672854569</v>
+        <v>62.79007800466752</v>
       </c>
       <c r="Q71">
-        <v>9.622278200216709</v>
+        <v>35.28168673412793</v>
       </c>
       <c r="R71">
-        <v>6.108903058258133</v>
+        <v>22.39931121361316</v>
       </c>
       <c r="S71">
-        <v>5.471853025999273</v>
+        <v>20.06346109533067</v>
       </c>
       <c r="T71">
-        <v>6.83692540700299</v>
+        <v>25.0687264923443</v>
       </c>
       <c r="U71">
-        <v>8.607551128160928</v>
+        <v>31.56102080325673</v>
       </c>
       <c r="V71">
-        <v>8.945946966387528</v>
+        <v>32.80180554342093</v>
       </c>
       <c r="W71">
-        <v>8.663940780062116</v>
+        <v>31.76778286022776</v>
       </c>
       <c r="X71">
-        <v>6.938177474819254</v>
+        <v>25.43998407433726</v>
       </c>
       <c r="Y71">
-        <v>14.18441470252098</v>
+        <v>52.00952057591027</v>
       </c>
       <c r="Z71">
-        <v>11.77907180701449</v>
+        <v>43.18992995905312</v>
       </c>
       <c r="AA71">
-        <v>7.609473338437544</v>
+        <v>27.90140224093766</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -6494,70 +6494,70 @@
         <v>69</v>
       </c>
       <c r="F72">
-        <v>22.860556731</v>
+        <v>83.82204134700001</v>
       </c>
       <c r="G72">
-        <v>30.97663263963</v>
+        <v>113.58098634531</v>
       </c>
       <c r="H72">
-        <v>33.21583657488</v>
+        <v>121.79140077456</v>
       </c>
       <c r="I72">
-        <v>38.91733828508</v>
+        <v>142.6969070452933</v>
       </c>
       <c r="J72">
-        <v>55.42842773779999</v>
+        <v>203.2375683719333</v>
       </c>
       <c r="K72">
-        <v>61.20581912982</v>
+        <v>224.42133680934</v>
       </c>
       <c r="L72">
-        <v>72.75787010825</v>
+        <v>266.7788570635834</v>
       </c>
       <c r="M72">
-        <v>81.5580822965</v>
+        <v>299.0463017538333</v>
       </c>
       <c r="N72">
-        <v>98.16805181739998</v>
+        <v>359.9495233304667</v>
       </c>
       <c r="O72">
-        <v>77.15539544444499</v>
+        <v>282.9031166296316</v>
       </c>
       <c r="P72">
-        <v>58.4628243552314</v>
+        <v>214.3636893025152</v>
       </c>
       <c r="Q72">
-        <v>44.21759800751593</v>
+        <v>162.1311926942251</v>
       </c>
       <c r="R72">
-        <v>34.07172575993715</v>
+        <v>124.9296611197695</v>
       </c>
       <c r="S72">
-        <v>30.37640324331296</v>
+        <v>111.3801452254808</v>
       </c>
       <c r="T72">
-        <v>32.88198059507673</v>
+        <v>120.567262181948</v>
       </c>
       <c r="U72">
-        <v>39.97735690589082</v>
+        <v>146.5836419882663</v>
       </c>
       <c r="V72">
-        <v>44.96388966528768</v>
+        <v>164.8675954393882</v>
       </c>
       <c r="W72">
-        <v>47.35363534744138</v>
+        <v>173.6299962739517</v>
       </c>
       <c r="X72">
-        <v>44.36555415594469</v>
+        <v>162.6736985717972</v>
       </c>
       <c r="Y72">
-        <v>37.05824326796628</v>
+        <v>135.8802253158764</v>
       </c>
       <c r="Z72">
-        <v>50.15449285868311</v>
+        <v>183.8998071485047</v>
       </c>
       <c r="AA72">
-        <v>35.91511258128122</v>
+        <v>131.6887461313645</v>
       </c>
     </row>
     <row r="73" spans="1:27">
@@ -6577,70 +6577,70 @@
         <v>69</v>
       </c>
       <c r="F73">
-        <v>11.54704905</v>
+        <v>42.33917985</v>
       </c>
       <c r="G73">
-        <v>27.5871312732</v>
+        <v>101.1528146684</v>
       </c>
       <c r="H73">
-        <v>41.6122021432</v>
+        <v>152.5780745250667</v>
       </c>
       <c r="I73">
-        <v>48.7586034824</v>
+        <v>178.7815461021333</v>
       </c>
       <c r="J73">
-        <v>53.5778487623</v>
+        <v>196.4521121284333</v>
       </c>
       <c r="K73">
-        <v>49.96180334465</v>
+        <v>183.1932789303833</v>
       </c>
       <c r="L73">
-        <v>48.7761036891</v>
+        <v>178.8457135267</v>
       </c>
       <c r="M73">
-        <v>49.332576064742</v>
+        <v>180.8861122373874</v>
       </c>
       <c r="N73">
-        <v>50.5482709285875</v>
+        <v>185.3436600714875</v>
       </c>
       <c r="O73">
-        <v>29.6871084809318</v>
+        <v>108.8527310967499</v>
       </c>
       <c r="P73">
-        <v>14.9342326120261</v>
+        <v>54.75885291076236</v>
       </c>
       <c r="Q73">
-        <v>4.086036087281058</v>
+        <v>14.98213232003055</v>
       </c>
       <c r="R73">
-        <v>-4.549897165352234</v>
+        <v>-16.68295627295819</v>
       </c>
       <c r="S73">
-        <v>-12.12673195008975</v>
+        <v>-44.46468381699574</v>
       </c>
       <c r="T73">
-        <v>-18.40686673701209</v>
+        <v>-67.49184470237766</v>
       </c>
       <c r="U73">
-        <v>-25.96740418060439</v>
+        <v>-95.21381532888277</v>
       </c>
       <c r="V73">
-        <v>-34.97266696393282</v>
+        <v>-128.233112201087</v>
       </c>
       <c r="W73">
-        <v>-45.36709152831285</v>
+        <v>-166.3460022704805</v>
       </c>
       <c r="X73">
-        <v>-59.91904342892133</v>
+        <v>-219.7031592393782</v>
       </c>
       <c r="Y73">
-        <v>-78.30374367776464</v>
+        <v>-287.1137268184704</v>
       </c>
       <c r="Z73">
-        <v>-95.53912621552765</v>
+        <v>-350.3101294569347</v>
       </c>
       <c r="AA73">
-        <v>-115.6364055343506</v>
+        <v>-424.000153625952</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -6660,70 +6660,70 @@
         <v>69</v>
       </c>
       <c r="F74">
-        <v>29.28685081</v>
+        <v>107.3851196366667</v>
       </c>
       <c r="G74">
-        <v>84.2464724391</v>
+        <v>308.9037322767</v>
       </c>
       <c r="H74">
-        <v>117.181117219</v>
+        <v>429.6640964696667</v>
       </c>
       <c r="I74">
-        <v>126.574947528</v>
+        <v>464.108140936</v>
       </c>
       <c r="J74">
-        <v>122.820126958</v>
+        <v>450.3404655126667</v>
       </c>
       <c r="K74">
-        <v>117.6822505352</v>
+        <v>431.5015852957333</v>
       </c>
       <c r="L74">
-        <v>137.9190872613002</v>
+        <v>505.7033199581007</v>
       </c>
       <c r="M74">
-        <v>138.8640115733416</v>
+        <v>509.168042435586</v>
       </c>
       <c r="N74">
-        <v>139.6485659666913</v>
+        <v>512.044741877868</v>
       </c>
       <c r="O74">
-        <v>76.89058590529464</v>
+        <v>281.9321483194137</v>
       </c>
       <c r="P74">
-        <v>59.18452637549662</v>
+        <v>217.0099300434876</v>
       </c>
       <c r="Q74">
-        <v>42.12165614973082</v>
+        <v>154.446072549013</v>
       </c>
       <c r="R74">
-        <v>25.15205272189603</v>
+        <v>92.22419331361876</v>
       </c>
       <c r="S74">
-        <v>9.408131732297781</v>
+        <v>34.4964830184252</v>
       </c>
       <c r="T74">
-        <v>-3.088503163344979</v>
+        <v>-11.32451159893159</v>
       </c>
       <c r="U74">
-        <v>-15.9545061178727</v>
+        <v>-58.49985576553325</v>
       </c>
       <c r="V74">
-        <v>-28.14473633714336</v>
+        <v>-103.1973665695256</v>
       </c>
       <c r="W74">
-        <v>-43.46183517562861</v>
+        <v>-159.3600623106382</v>
       </c>
       <c r="X74">
-        <v>-63.86875543216812</v>
+        <v>-234.1854365846164</v>
       </c>
       <c r="Y74">
-        <v>-90.20039172666723</v>
+        <v>-330.7347696644466</v>
       </c>
       <c r="Z74">
-        <v>-118.242646307418</v>
+        <v>-433.556369793866</v>
       </c>
       <c r="AA74">
-        <v>-149.9407850193919</v>
+        <v>-549.7828784044369</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6743,70 +6743,70 @@
         <v>69</v>
       </c>
       <c r="F75">
-        <v>26.92539474</v>
+        <v>98.72644738000001</v>
       </c>
       <c r="G75">
-        <v>60.48794375234</v>
+        <v>221.7891270919133</v>
       </c>
       <c r="H75">
-        <v>99.26631382559999</v>
+        <v>363.9764840272</v>
       </c>
       <c r="I75">
-        <v>117.7811917316</v>
+        <v>431.8643696825334</v>
       </c>
       <c r="J75">
-        <v>140.179054265</v>
+        <v>513.9898656383333</v>
       </c>
       <c r="K75">
-        <v>133.9896748012</v>
+        <v>491.2954742710667</v>
       </c>
       <c r="L75">
-        <v>139.6261193277</v>
+        <v>511.9624375348999</v>
       </c>
       <c r="M75">
-        <v>142.48412675956</v>
+        <v>522.4417981183867</v>
       </c>
       <c r="N75">
-        <v>150.84721799004</v>
+        <v>553.10646596348</v>
       </c>
       <c r="O75">
-        <v>83.87000587430001</v>
+        <v>307.5233548724333</v>
       </c>
       <c r="P75">
-        <v>44.54758066640262</v>
+        <v>163.341129110143</v>
       </c>
       <c r="Q75">
-        <v>10.11339379799618</v>
+        <v>37.08244392598601</v>
       </c>
       <c r="R75">
-        <v>-24.78607977745955</v>
+        <v>-90.88229251735167</v>
       </c>
       <c r="S75">
-        <v>-57.64480321884018</v>
+        <v>-211.3642784690807</v>
       </c>
       <c r="T75">
-        <v>-83.86245931175631</v>
+        <v>-307.4956841431065</v>
       </c>
       <c r="U75">
-        <v>-108.0360248416964</v>
+        <v>-396.1320910862202</v>
       </c>
       <c r="V75">
-        <v>-133.8943280181178</v>
+        <v>-490.9458693997651</v>
       </c>
       <c r="W75">
-        <v>-162.6484364179364</v>
+        <v>-596.3776001990999</v>
       </c>
       <c r="X75">
-        <v>-198.1848048181328</v>
+        <v>-726.677617666487</v>
       </c>
       <c r="Y75">
-        <v>-246.5704987087828</v>
+        <v>-904.0918285988705</v>
       </c>
       <c r="Z75">
-        <v>-294.9332923104827</v>
+        <v>-1081.422071805103</v>
       </c>
       <c r="AA75">
-        <v>-351.6766012392087</v>
+        <v>-1289.480871210432</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6826,70 +6826,70 @@
         <v>69</v>
       </c>
       <c r="F76">
-        <v>55.12194158</v>
+        <v>202.1137857933333</v>
       </c>
       <c r="G76">
-        <v>120.210906461</v>
+        <v>440.7733236903333</v>
       </c>
       <c r="H76">
-        <v>160.662459613</v>
+        <v>589.0956852476667</v>
       </c>
       <c r="I76">
-        <v>155.493415164</v>
+        <v>570.142522268</v>
       </c>
       <c r="J76">
-        <v>165.293038857</v>
+        <v>606.074475809</v>
       </c>
       <c r="K76">
-        <v>162.740458593</v>
+        <v>596.715014841</v>
       </c>
       <c r="L76">
-        <v>180.08926626292</v>
+        <v>660.3273096307067</v>
       </c>
       <c r="M76">
-        <v>180.119148782225</v>
+        <v>660.4368788681584</v>
       </c>
       <c r="N76">
-        <v>181.861939585569</v>
+        <v>666.8271118137529</v>
       </c>
       <c r="O76">
-        <v>103.226799718487</v>
+        <v>378.4982656344523</v>
       </c>
       <c r="P76">
-        <v>58.529036573288</v>
+        <v>214.6064674353894</v>
       </c>
       <c r="Q76">
-        <v>36.56560799817306</v>
+        <v>134.0738959933012</v>
       </c>
       <c r="R76">
-        <v>13.34895068253516</v>
+        <v>48.94615250262891</v>
       </c>
       <c r="S76">
-        <v>-5.204360487415164</v>
+        <v>-19.08265512052226</v>
       </c>
       <c r="T76">
-        <v>-16.69052619318921</v>
+        <v>-61.19859604169378</v>
       </c>
       <c r="U76">
-        <v>-24.13683209991486</v>
+        <v>-88.5017176996878</v>
       </c>
       <c r="V76">
-        <v>-26.73905336906643</v>
+        <v>-98.04319568657691</v>
       </c>
       <c r="W76">
-        <v>-28.21973128733085</v>
+        <v>-103.4723480535465</v>
       </c>
       <c r="X76">
-        <v>-30.54635651135812</v>
+        <v>-112.0033072083131</v>
       </c>
       <c r="Y76">
-        <v>-31.68479824649337</v>
+        <v>-116.1775935704757</v>
       </c>
       <c r="Z76">
-        <v>-33.74126472307793</v>
+        <v>-123.7179706512857</v>
       </c>
       <c r="AA76">
-        <v>-37.72455296431362</v>
+        <v>-138.3233608691499</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6909,70 +6909,70 @@
         <v>69</v>
       </c>
       <c r="F77">
-        <v>11.2100710294036</v>
+        <v>41.10359377447987</v>
       </c>
       <c r="G77">
-        <v>31.122462663253</v>
+        <v>114.1156964319277</v>
       </c>
       <c r="H77">
-        <v>46.914597290169</v>
+        <v>172.020190063953</v>
       </c>
       <c r="I77">
-        <v>53.325731609493</v>
+        <v>195.527682568141</v>
       </c>
       <c r="J77">
-        <v>57.46169756462</v>
+        <v>210.6928910702734</v>
       </c>
       <c r="K77">
-        <v>53.117951993791</v>
+        <v>194.7658239772337</v>
       </c>
       <c r="L77">
-        <v>55.86227052748</v>
+        <v>204.8283252674267</v>
       </c>
       <c r="M77">
-        <v>58.548530458943</v>
+        <v>214.6779450161243</v>
       </c>
       <c r="N77">
-        <v>62.338248653344</v>
+        <v>228.5735783955947</v>
       </c>
       <c r="O77">
-        <v>36.769638392241</v>
+        <v>134.822007438217</v>
       </c>
       <c r="P77">
-        <v>18.0675394298295</v>
+        <v>66.24764457604149</v>
       </c>
       <c r="Q77">
-        <v>2.15860550968747</v>
+        <v>7.914886868854057</v>
       </c>
       <c r="R77">
-        <v>-13.32884758456481</v>
+        <v>-48.87244114340432</v>
       </c>
       <c r="S77">
-        <v>-26.83138265962117</v>
+        <v>-98.38173641861096</v>
       </c>
       <c r="T77">
-        <v>-38.69066094558481</v>
+        <v>-141.8657568004776</v>
       </c>
       <c r="U77">
-        <v>-50.67968794336908</v>
+        <v>-185.82552245902</v>
       </c>
       <c r="V77">
-        <v>-60.36367444451269</v>
+        <v>-221.3334729632132</v>
       </c>
       <c r="W77">
-        <v>-67.10740113734255</v>
+        <v>-246.0604708369227</v>
       </c>
       <c r="X77">
-        <v>-72.93549736616698</v>
+        <v>-267.430157009279</v>
       </c>
       <c r="Y77">
-        <v>-75.68539964091671</v>
+        <v>-277.5131320166946</v>
       </c>
       <c r="Z77">
-        <v>-76.79373107974949</v>
+        <v>-281.5770139590815</v>
       </c>
       <c r="AA77">
-        <v>-74.26527833420437</v>
+        <v>-272.3060205587494</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6992,70 +6992,70 @@
         <v>69</v>
       </c>
       <c r="F78">
-        <v>65.09281855</v>
+        <v>238.6736680166667</v>
       </c>
       <c r="G78">
-        <v>157.1541007854</v>
+        <v>576.2317028798001</v>
       </c>
       <c r="H78">
-        <v>115.222417852</v>
+        <v>422.4821987906667</v>
       </c>
       <c r="I78">
-        <v>138.322717767</v>
+        <v>507.183298479</v>
       </c>
       <c r="J78">
-        <v>121.50226065</v>
+        <v>445.50828905</v>
       </c>
       <c r="K78">
-        <v>141.959463474</v>
+        <v>520.518032738</v>
       </c>
       <c r="L78">
-        <v>151.432908404874</v>
+        <v>555.253997484538</v>
       </c>
       <c r="M78">
-        <v>156.976801022152</v>
+        <v>575.5816037478907</v>
       </c>
       <c r="N78">
-        <v>162.977795004884</v>
+        <v>597.5852483512414</v>
       </c>
       <c r="O78">
-        <v>94.555568048363</v>
+        <v>346.7037495106643</v>
       </c>
       <c r="P78">
-        <v>67.4431918507818</v>
+        <v>247.2917034528666</v>
       </c>
       <c r="Q78">
-        <v>46.6775796211314</v>
+        <v>171.1511252774818</v>
       </c>
       <c r="R78">
-        <v>30.27903566230068</v>
+        <v>111.0231307617692</v>
       </c>
       <c r="S78">
-        <v>14.67171476777385</v>
+        <v>53.79628748183745</v>
       </c>
       <c r="T78">
-        <v>1.012523478036656</v>
+        <v>3.712586086134404</v>
       </c>
       <c r="U78">
-        <v>-13.40017876046258</v>
+        <v>-49.13398878836281</v>
       </c>
       <c r="V78">
-        <v>-29.16946549728238</v>
+        <v>-106.9547068233687</v>
       </c>
       <c r="W78">
-        <v>-46.06279448336478</v>
+        <v>-168.8969131056709</v>
       </c>
       <c r="X78">
-        <v>-70.55751635041884</v>
+        <v>-258.7108932848691</v>
       </c>
       <c r="Y78">
-        <v>-96.75203053004846</v>
+        <v>-354.7574452768443</v>
       </c>
       <c r="Z78">
-        <v>-120.8455277390867</v>
+        <v>-443.1002683766512</v>
       </c>
       <c r="AA78">
-        <v>-152.6927090485523</v>
+        <v>-559.8732665113586</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -7075,70 +7075,70 @@
         <v>69</v>
       </c>
       <c r="F79">
-        <v>199.4040951</v>
+        <v>731.1483487</v>
       </c>
       <c r="G79">
-        <v>706.64431908502</v>
+        <v>2591.029169978407</v>
       </c>
       <c r="H79">
-        <v>1839.5118966448</v>
+        <v>6744.876954364267</v>
       </c>
       <c r="I79">
-        <v>2652.8656639431</v>
+        <v>9727.174101124701</v>
       </c>
       <c r="J79">
-        <v>3079.6009821626</v>
+        <v>11291.87026792953</v>
       </c>
       <c r="K79">
-        <v>3478.81594453961</v>
+        <v>12755.6584633119</v>
       </c>
       <c r="L79">
-        <v>3858.646748044429</v>
+        <v>14148.37140949624</v>
       </c>
       <c r="M79">
-        <v>3894.360027938582</v>
+        <v>14279.32010244147</v>
       </c>
       <c r="N79">
-        <v>3865.810264789333</v>
+        <v>14174.63763756089</v>
       </c>
       <c r="O79">
-        <v>1480.10144716593</v>
+        <v>5427.038639608411</v>
       </c>
       <c r="P79">
-        <v>713.0282151847026</v>
+        <v>2614.436789010576</v>
       </c>
       <c r="Q79">
-        <v>300.2960845298022</v>
+        <v>1101.085643275941</v>
       </c>
       <c r="R79">
-        <v>18.38215125808541</v>
+        <v>67.40122127964651</v>
       </c>
       <c r="S79">
-        <v>-190.7631764292504</v>
+        <v>-699.4649802405847</v>
       </c>
       <c r="T79">
-        <v>-346.415247804918</v>
+        <v>-1270.189241951366</v>
       </c>
       <c r="U79">
-        <v>-509.3470015725304</v>
+        <v>-1867.605672432612</v>
       </c>
       <c r="V79">
-        <v>-598.0619867729422</v>
+        <v>-2192.893951500788</v>
       </c>
       <c r="W79">
-        <v>-652.426655353833</v>
+        <v>-2392.231069630721</v>
       </c>
       <c r="X79">
-        <v>-684.5706971552613</v>
+        <v>-2510.092556235958</v>
       </c>
       <c r="Y79">
-        <v>-687.6046176659221</v>
+        <v>-2521.216931441714</v>
       </c>
       <c r="Z79">
-        <v>-682.292697548917</v>
+        <v>-2501.739891012695</v>
       </c>
       <c r="AA79">
-        <v>-714.452104825559</v>
+        <v>-2619.657717693716</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -7158,70 +7158,70 @@
         <v>69</v>
       </c>
       <c r="F80">
-        <v>6.135872179</v>
+        <v>22.49819798966666</v>
       </c>
       <c r="G80">
-        <v>15.7942725306</v>
+        <v>57.9123326122</v>
       </c>
       <c r="H80">
-        <v>18.11854172</v>
+        <v>66.43465297333333</v>
       </c>
       <c r="I80">
-        <v>21.833005389</v>
+        <v>80.054353093</v>
       </c>
       <c r="J80">
-        <v>27.447622871</v>
+        <v>100.6412838603333</v>
       </c>
       <c r="K80">
-        <v>27.241888482</v>
+        <v>99.88692443399999</v>
       </c>
       <c r="L80">
-        <v>30.1220909911</v>
+        <v>110.4476669673667</v>
       </c>
       <c r="M80">
-        <v>31.761766533359</v>
+        <v>116.4598106223163</v>
       </c>
       <c r="N80">
-        <v>34.274787034104</v>
+        <v>125.674219125048</v>
       </c>
       <c r="O80">
-        <v>19.830519149103</v>
+        <v>72.711903546711</v>
       </c>
       <c r="P80">
-        <v>10.510786995665</v>
+        <v>38.53955231743834</v>
       </c>
       <c r="Q80">
-        <v>2.711312864826869</v>
+        <v>9.941480504365186</v>
       </c>
       <c r="R80">
-        <v>-4.010412893396711</v>
+        <v>-14.70484727578794</v>
       </c>
       <c r="S80">
-        <v>-9.838802402041932</v>
+        <v>-36.07560880748708</v>
       </c>
       <c r="T80">
-        <v>-14.62830089344762</v>
+        <v>-53.6371032759746</v>
       </c>
       <c r="U80">
-        <v>-20.04022930989466</v>
+        <v>-73.48084080294707</v>
       </c>
       <c r="V80">
-        <v>-25.87536598514086</v>
+        <v>-94.87634194551647</v>
       </c>
       <c r="W80">
-        <v>-31.50854990324867</v>
+        <v>-115.5313496452451</v>
       </c>
       <c r="X80">
-        <v>-38.5084962934073</v>
+        <v>-141.1978197424935</v>
       </c>
       <c r="Y80">
-        <v>-46.44812545598441</v>
+        <v>-170.3097933386095</v>
       </c>
       <c r="Z80">
-        <v>-53.59251861854534</v>
+        <v>-196.5059016013329</v>
       </c>
       <c r="AA80">
-        <v>-59.13857545525666</v>
+        <v>-216.8414433359411</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -7241,70 +7241,70 @@
         <v>69</v>
       </c>
       <c r="F81">
-        <v>131.704263407</v>
+        <v>482.9156324923333</v>
       </c>
       <c r="G81">
-        <v>282.850500476</v>
+        <v>1037.118501745333</v>
       </c>
       <c r="H81">
-        <v>210.485102924</v>
+        <v>771.7787107213334</v>
       </c>
       <c r="I81">
-        <v>205.5846233015</v>
+        <v>753.8102854388334</v>
       </c>
       <c r="J81">
-        <v>189.7968319907</v>
+        <v>695.9217172992334</v>
       </c>
       <c r="K81">
-        <v>188.0197045795</v>
+        <v>689.4055834581667</v>
       </c>
       <c r="L81">
-        <v>202.4885030229</v>
+        <v>742.4578444173</v>
       </c>
       <c r="M81">
-        <v>201.936475463962</v>
+        <v>740.4337433678606</v>
       </c>
       <c r="N81">
-        <v>199.443546438701</v>
+        <v>731.2930036085703</v>
       </c>
       <c r="O81">
-        <v>99.88727870079768</v>
+        <v>366.2533552362581</v>
       </c>
       <c r="P81">
-        <v>63.96238279099666</v>
+        <v>234.5287369003211</v>
       </c>
       <c r="Q81">
-        <v>43.5585149205649</v>
+        <v>159.714554708738</v>
       </c>
       <c r="R81">
-        <v>33.65470960665763</v>
+        <v>123.400601891078</v>
       </c>
       <c r="S81">
-        <v>29.12199272332229</v>
+        <v>106.7806399855151</v>
       </c>
       <c r="T81">
-        <v>25.24677671953496</v>
+        <v>92.57151463829486</v>
       </c>
       <c r="U81">
-        <v>21.48656963061465</v>
+        <v>78.78408864558706</v>
       </c>
       <c r="V81">
-        <v>18.37936668591695</v>
+        <v>67.39101118169548</v>
       </c>
       <c r="W81">
-        <v>15.45891678079367</v>
+        <v>56.68269486291013</v>
       </c>
       <c r="X81">
-        <v>11.99894108059613</v>
+        <v>43.99611729551916</v>
       </c>
       <c r="Y81">
-        <v>8.552204396628609</v>
+        <v>31.35808278763824</v>
       </c>
       <c r="Z81">
-        <v>5.29605378122572</v>
+        <v>19.41886386449431</v>
       </c>
       <c r="AA81">
-        <v>2.287909047134298</v>
+        <v>8.388999839492426</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -7324,70 +7324,70 @@
         <v>69</v>
       </c>
       <c r="F82">
-        <v>416.8498639239</v>
+        <v>1528.4495010543</v>
       </c>
       <c r="G82">
-        <v>931.175059547</v>
+        <v>3414.308551672334</v>
       </c>
       <c r="H82">
-        <v>979.573340683</v>
+        <v>3591.768915837667</v>
       </c>
       <c r="I82">
-        <v>890.880026408</v>
+        <v>3266.560096829333</v>
       </c>
       <c r="J82">
-        <v>797.832774611</v>
+        <v>2925.386840240333</v>
       </c>
       <c r="K82">
-        <v>684.474139468</v>
+        <v>2509.738511382666</v>
       </c>
       <c r="L82">
-        <v>697.55274187591</v>
+        <v>2557.693386878337</v>
       </c>
       <c r="M82">
-        <v>678.125083679018</v>
+        <v>2486.458640156399</v>
       </c>
       <c r="N82">
-        <v>662.7527707655</v>
+        <v>2430.093492806833</v>
       </c>
       <c r="O82">
-        <v>386.8461187908758</v>
+        <v>1418.435768899878</v>
       </c>
       <c r="P82">
-        <v>271.5632754678829</v>
+        <v>995.7320100489042</v>
       </c>
       <c r="Q82">
-        <v>175.7755552070184</v>
+        <v>644.5103690924007</v>
       </c>
       <c r="R82">
-        <v>156.514521972458</v>
+        <v>573.8865805656793</v>
       </c>
       <c r="S82">
-        <v>152.3609027712552</v>
+        <v>558.6566434946025</v>
       </c>
       <c r="T82">
-        <v>141.7889253415948</v>
+        <v>519.8927262525143</v>
       </c>
       <c r="U82">
-        <v>126.8257659546066</v>
+        <v>465.0278085002242</v>
       </c>
       <c r="V82">
-        <v>117.3808172700346</v>
+        <v>430.3963299901268</v>
       </c>
       <c r="W82">
-        <v>106.2802643560607</v>
+        <v>389.6943026388894</v>
       </c>
       <c r="X82">
-        <v>93.26346674304696</v>
+        <v>341.9660447245055</v>
       </c>
       <c r="Y82">
-        <v>76.59426324226926</v>
+        <v>280.8456318883206</v>
       </c>
       <c r="Z82">
-        <v>72.36625033714397</v>
+        <v>265.3429179028612</v>
       </c>
       <c r="AA82">
-        <v>60.35356496964448</v>
+        <v>221.2964048886964</v>
       </c>
     </row>
     <row r="83" spans="1:27">
@@ -7407,70 +7407,70 @@
         <v>69</v>
       </c>
       <c r="F83">
-        <v>37.805100058</v>
+        <v>138.6187002126667</v>
       </c>
       <c r="G83">
-        <v>113.071279975</v>
+        <v>414.5946932416666</v>
       </c>
       <c r="H83">
-        <v>117.12130277731</v>
+        <v>429.4447768501366</v>
       </c>
       <c r="I83">
-        <v>134.6139363766</v>
+        <v>493.5844333808666</v>
       </c>
       <c r="J83">
-        <v>147.9962126795</v>
+        <v>542.6527798248334</v>
       </c>
       <c r="K83">
-        <v>167.5352937504</v>
+        <v>614.2960770848</v>
       </c>
       <c r="L83">
-        <v>194.65563035619</v>
+        <v>713.7373113060299</v>
       </c>
       <c r="M83">
-        <v>209.48414834546</v>
+        <v>768.1085439333533</v>
       </c>
       <c r="N83">
-        <v>221.53331477226</v>
+        <v>812.28882083162</v>
       </c>
       <c r="O83">
-        <v>135.7815042838007</v>
+        <v>497.8655157072693</v>
       </c>
       <c r="P83">
-        <v>94.3683556627245</v>
+        <v>346.0173040966565</v>
       </c>
       <c r="Q83">
-        <v>70.58513175367655</v>
+        <v>258.8121497634807</v>
       </c>
       <c r="R83">
-        <v>61.95041745518545</v>
+        <v>227.1515306690133</v>
       </c>
       <c r="S83">
-        <v>57.0351676034341</v>
+        <v>209.1289478792584</v>
       </c>
       <c r="T83">
-        <v>52.32737614210357</v>
+        <v>191.8670458543797</v>
       </c>
       <c r="U83">
-        <v>47.5294207231469</v>
+        <v>174.2745426515386</v>
       </c>
       <c r="V83">
-        <v>42.99446129582498</v>
+        <v>157.6463580846916</v>
       </c>
       <c r="W83">
-        <v>38.21922001229224</v>
+        <v>140.1371400450716</v>
       </c>
       <c r="X83">
-        <v>33.33292309630156</v>
+        <v>122.2207180197724</v>
       </c>
       <c r="Y83">
-        <v>27.56471076244554</v>
+        <v>101.070606128967</v>
       </c>
       <c r="Z83">
-        <v>19.78760590681228</v>
+        <v>72.55455499164503</v>
       </c>
       <c r="AA83">
-        <v>13.40318925659928</v>
+        <v>49.14502727419737</v>
       </c>
     </row>
     <row r="84" spans="1:27">
@@ -7490,70 +7490,70 @@
         <v>69</v>
       </c>
       <c r="F84">
-        <v>11.976397889</v>
+        <v>43.91345892633333</v>
       </c>
       <c r="G84">
-        <v>21.76024062437</v>
+        <v>79.78754895602333</v>
       </c>
       <c r="H84">
-        <v>24.6177736181</v>
+        <v>90.26516993303333</v>
       </c>
       <c r="I84">
-        <v>25.4130228792</v>
+        <v>93.18108389039999</v>
       </c>
       <c r="J84">
-        <v>23.9233616458</v>
+        <v>87.71899270126666</v>
       </c>
       <c r="K84">
-        <v>20.5572363508</v>
+        <v>75.37653328626666</v>
       </c>
       <c r="L84">
-        <v>21.85989287321</v>
+        <v>80.15294053510333</v>
       </c>
       <c r="M84">
-        <v>22.0061945598509</v>
+        <v>80.68938005278663</v>
       </c>
       <c r="N84">
-        <v>23.4716648920859</v>
+        <v>86.06277127098163</v>
       </c>
       <c r="O84">
-        <v>8.0040972578522</v>
+        <v>29.34835661212473</v>
       </c>
       <c r="P84">
-        <v>2.906242331618161</v>
+        <v>10.65622188259992</v>
       </c>
       <c r="Q84">
-        <v>0.0453164782284085</v>
+        <v>0.1661604201708312</v>
       </c>
       <c r="R84">
-        <v>-1.805202224845626</v>
+        <v>-6.619074824433962</v>
       </c>
       <c r="S84">
-        <v>-3.12084994089622</v>
+        <v>-11.44311644995281</v>
       </c>
       <c r="T84">
-        <v>-3.507549308987473</v>
+        <v>-12.86101413295407</v>
       </c>
       <c r="U84">
-        <v>-2.653942723459168</v>
+        <v>-9.731123319350283</v>
       </c>
       <c r="V84">
-        <v>-1.640986365895647</v>
+        <v>-6.016950008284037</v>
       </c>
       <c r="W84">
-        <v>-1.393899759111925</v>
+        <v>-5.110965783410391</v>
       </c>
       <c r="X84">
-        <v>-1.710144543430045</v>
+        <v>-6.27052999257683</v>
       </c>
       <c r="Y84">
-        <v>-1.842577505699234</v>
+        <v>-6.756117520897192</v>
       </c>
       <c r="Z84">
-        <v>-2.05133623922913</v>
+        <v>-7.521566210506811</v>
       </c>
       <c r="AA84">
-        <v>-2.063257477350279</v>
+        <v>-7.565277416951024</v>
       </c>
     </row>
     <row r="85" spans="1:27">
@@ -7573,70 +7573,70 @@
         <v>69</v>
       </c>
       <c r="F85">
-        <v>34.557224208</v>
+        <v>126.709822096</v>
       </c>
       <c r="G85">
-        <v>163.5671125841</v>
+        <v>599.7460794750333</v>
       </c>
       <c r="H85">
-        <v>340.7732727852</v>
+        <v>1249.5020002124</v>
       </c>
       <c r="I85">
-        <v>492.3933979159</v>
+        <v>1805.442459024967</v>
       </c>
       <c r="J85">
-        <v>636.596034527</v>
+        <v>2334.185459932334</v>
       </c>
       <c r="K85">
-        <v>700.918416581</v>
+        <v>2570.034194130333</v>
       </c>
       <c r="L85">
-        <v>756.839157981</v>
+        <v>2775.076912597</v>
       </c>
       <c r="M85">
-        <v>863.745887100642</v>
+        <v>3167.068252702354</v>
       </c>
       <c r="N85">
-        <v>961.986510506816</v>
+        <v>3527.283871858326</v>
       </c>
       <c r="O85">
-        <v>488.99605908982</v>
+        <v>1792.985549996007</v>
       </c>
       <c r="P85">
-        <v>271.78009105095</v>
+        <v>996.5270005201501</v>
       </c>
       <c r="Q85">
-        <v>191.054055191805</v>
+        <v>700.5315357032852</v>
       </c>
       <c r="R85">
-        <v>172.240944623215</v>
+        <v>631.5501302851217</v>
       </c>
       <c r="S85">
-        <v>159.6987133869044</v>
+        <v>585.5619490853161</v>
       </c>
       <c r="T85">
-        <v>142.5593372325681</v>
+        <v>522.7175698527496</v>
       </c>
       <c r="U85">
-        <v>116.354271983038</v>
+        <v>426.6323306044727</v>
       </c>
       <c r="V85">
-        <v>91.24173230747684</v>
+        <v>334.5530184607484</v>
       </c>
       <c r="W85">
-        <v>69.48322500407744</v>
+        <v>254.7718250149506</v>
       </c>
       <c r="X85">
-        <v>86.72650529661328</v>
+        <v>317.9971860875821</v>
       </c>
       <c r="Y85">
-        <v>70.23889340330332</v>
+        <v>257.5426091454455</v>
       </c>
       <c r="Z85">
-        <v>57.42921862508466</v>
+        <v>210.5738016253104</v>
       </c>
       <c r="AA85">
-        <v>48.26375081433664</v>
+        <v>176.9670863192343</v>
       </c>
     </row>
     <row r="86" spans="1:27">
@@ -7656,70 +7656,70 @@
         <v>69</v>
       </c>
       <c r="F86">
-        <v>7.99434294</v>
+        <v>29.31259078</v>
       </c>
       <c r="G86">
-        <v>44.5699592992</v>
+        <v>163.4231840970667</v>
       </c>
       <c r="H86">
-        <v>99.6257825818</v>
+        <v>365.2945361332666</v>
       </c>
       <c r="I86">
-        <v>121.468212781</v>
+        <v>445.3834468636667</v>
       </c>
       <c r="J86">
-        <v>139.793840632</v>
+        <v>512.5774156506667</v>
       </c>
       <c r="K86">
-        <v>167.163024052</v>
+        <v>612.9310881906666</v>
       </c>
       <c r="L86">
-        <v>172.9968705643</v>
+        <v>634.3218587357667</v>
       </c>
       <c r="M86">
-        <v>192.4195292929138</v>
+        <v>705.5382740740173</v>
       </c>
       <c r="N86">
-        <v>207.882258939329</v>
+        <v>762.2349494442063</v>
       </c>
       <c r="O86">
-        <v>99.39938463006</v>
+        <v>364.46441031022</v>
       </c>
       <c r="P86">
-        <v>55.653540448766</v>
+        <v>204.0629816454753</v>
       </c>
       <c r="Q86">
-        <v>31.30483234110845</v>
+        <v>114.784385250731</v>
       </c>
       <c r="R86">
-        <v>25.45756654177295</v>
+        <v>93.34441065316749</v>
       </c>
       <c r="S86">
-        <v>19.74359991324106</v>
+        <v>72.39319968188387</v>
       </c>
       <c r="T86">
-        <v>13.53496175466828</v>
+        <v>49.62819310045035</v>
       </c>
       <c r="U86">
-        <v>11.61738239711549</v>
+        <v>42.59706878942345</v>
       </c>
       <c r="V86">
-        <v>17.02821119638817</v>
+        <v>62.43677438675664</v>
       </c>
       <c r="W86">
-        <v>13.08122564366091</v>
+        <v>47.96449402675668</v>
       </c>
       <c r="X86">
-        <v>9.594174135729654</v>
+        <v>35.1786384976754</v>
       </c>
       <c r="Y86">
-        <v>6.606540805231735</v>
+        <v>24.22398295251636</v>
       </c>
       <c r="Z86">
-        <v>3.645557611198165</v>
+        <v>13.36704457439327</v>
       </c>
       <c r="AA86">
-        <v>0.9545365842795496</v>
+        <v>3.499967475691682</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -7739,70 +7739,70 @@
         <v>69</v>
       </c>
       <c r="F87">
-        <v>144.07195037</v>
+        <v>528.2638180233333</v>
       </c>
       <c r="G87">
-        <v>314.833747204</v>
+        <v>1154.390406414667</v>
       </c>
       <c r="H87">
-        <v>352.1700565938</v>
+        <v>1291.2902075106</v>
       </c>
       <c r="I87">
-        <v>327.1862158525</v>
+        <v>1199.682791459167</v>
       </c>
       <c r="J87">
-        <v>330.31564201089</v>
+        <v>1211.15735403993</v>
       </c>
       <c r="K87">
-        <v>284.64527130811</v>
+        <v>1043.699328129737</v>
       </c>
       <c r="L87">
-        <v>315.7080457570198</v>
+        <v>1157.596167775739</v>
       </c>
       <c r="M87">
-        <v>306.6723026269224</v>
+        <v>1124.465109632049</v>
       </c>
       <c r="N87">
-        <v>294.9613927579666</v>
+        <v>1081.525106779211</v>
       </c>
       <c r="O87">
-        <v>165.3400748084321</v>
+        <v>606.2469409642512</v>
       </c>
       <c r="P87">
-        <v>97.77849453057588</v>
+        <v>358.5211466121116</v>
       </c>
       <c r="Q87">
-        <v>55.66355057947226</v>
+        <v>204.099685458065</v>
       </c>
       <c r="R87">
-        <v>30.42035732538928</v>
+        <v>111.541310193094</v>
       </c>
       <c r="S87">
-        <v>17.57207612979361</v>
+        <v>64.43094580924324</v>
       </c>
       <c r="T87">
-        <v>11.00844392701663</v>
+        <v>40.36429439906099</v>
       </c>
       <c r="U87">
-        <v>9.311755826884928</v>
+        <v>34.14310469857807</v>
       </c>
       <c r="V87">
-        <v>9.355333271031045</v>
+        <v>34.30288866044716</v>
       </c>
       <c r="W87">
-        <v>10.92291794930008</v>
+        <v>40.05069914743361</v>
       </c>
       <c r="X87">
-        <v>12.9654760414277</v>
+        <v>47.54007881856822</v>
       </c>
       <c r="Y87">
-        <v>13.77474010489118</v>
+        <v>50.50738038460099</v>
       </c>
       <c r="Z87">
-        <v>12.86288275674709</v>
+        <v>47.163903441406</v>
       </c>
       <c r="AA87">
-        <v>10.57810376735257</v>
+        <v>38.78638048029276</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -7822,70 +7822,70 @@
         <v>69</v>
       </c>
       <c r="F88">
-        <v>25.931869671</v>
+        <v>95.08352212699999</v>
       </c>
       <c r="G88">
-        <v>82.285989926</v>
+        <v>301.7152963953333</v>
       </c>
       <c r="H88">
-        <v>127.368707052</v>
+        <v>467.018592524</v>
       </c>
       <c r="I88">
-        <v>134.812316285</v>
+        <v>494.3118263783334</v>
       </c>
       <c r="J88">
-        <v>137.7236465</v>
+        <v>504.9867038333334</v>
       </c>
       <c r="K88">
-        <v>113.71364008</v>
+        <v>416.9500136266667</v>
       </c>
       <c r="L88">
-        <v>117.527243323</v>
+        <v>430.9332255176666</v>
       </c>
       <c r="M88">
-        <v>119.348551037236</v>
+        <v>437.6113538031987</v>
       </c>
       <c r="N88">
-        <v>125.108078934595</v>
+        <v>458.7296227601817</v>
       </c>
       <c r="O88">
-        <v>76.847959221876</v>
+        <v>281.775850480212</v>
       </c>
       <c r="P88">
-        <v>46.1909259457501</v>
+        <v>169.3667284677503</v>
       </c>
       <c r="Q88">
-        <v>24.49211600200358</v>
+        <v>89.80442534067981</v>
       </c>
       <c r="R88">
-        <v>7.133675423962691</v>
+        <v>26.1568098878632</v>
       </c>
       <c r="S88">
-        <v>-7.186988482499226</v>
+        <v>-26.35229110249716</v>
       </c>
       <c r="T88">
-        <v>-17.89015537944533</v>
+        <v>-65.59723639129955</v>
       </c>
       <c r="U88">
-        <v>-28.13249423670137</v>
+        <v>-103.152478867905</v>
       </c>
       <c r="V88">
-        <v>-38.74072231144891</v>
+        <v>-142.0493151419793</v>
       </c>
       <c r="W88">
-        <v>-51.46450996826594</v>
+        <v>-188.7032032169751</v>
       </c>
       <c r="X88">
-        <v>-68.17179631166255</v>
+        <v>-249.9632531427627</v>
       </c>
       <c r="Y88">
-        <v>-84.599841312564</v>
+        <v>-310.199418146068</v>
       </c>
       <c r="Z88">
-        <v>-97.3945746624206</v>
+        <v>-357.1134404288755</v>
       </c>
       <c r="AA88">
-        <v>-108.5263258696281</v>
+        <v>-397.9298615219696</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -7905,70 +7905,70 @@
         <v>69</v>
       </c>
       <c r="F89">
-        <v>93.8217636</v>
+        <v>344.0131332</v>
       </c>
       <c r="G89">
-        <v>201.359352363</v>
+        <v>738.3176253309999</v>
       </c>
       <c r="H89">
-        <v>388.508470137</v>
+        <v>1424.531057169</v>
       </c>
       <c r="I89">
-        <v>501.038532346</v>
+        <v>1837.141285268667</v>
       </c>
       <c r="J89">
-        <v>588.125786353</v>
+        <v>2156.461216627667</v>
       </c>
       <c r="K89">
-        <v>607.3209548250001</v>
+        <v>2226.843501025</v>
       </c>
       <c r="L89">
-        <v>619.5179006607</v>
+        <v>2271.5656357559</v>
       </c>
       <c r="M89">
-        <v>645.9277283192</v>
+        <v>2368.401670503733</v>
       </c>
       <c r="N89">
-        <v>681.6840100013</v>
+        <v>2499.508036671433</v>
       </c>
       <c r="O89">
-        <v>489.1579324297768</v>
+        <v>1793.579085575848</v>
       </c>
       <c r="P89">
-        <v>337.2656939306884</v>
+        <v>1236.640877745858</v>
       </c>
       <c r="Q89">
-        <v>235.2637537830471</v>
+        <v>862.6337638711726</v>
       </c>
       <c r="R89">
-        <v>154.2736843558435</v>
+        <v>565.6701759714261</v>
       </c>
       <c r="S89">
-        <v>85.90809533535148</v>
+        <v>314.9963495629554</v>
       </c>
       <c r="T89">
-        <v>37.28571549225971</v>
+        <v>136.7142901382856</v>
       </c>
       <c r="U89">
-        <v>-0.3110933780161824</v>
+        <v>-1.140675719392669</v>
       </c>
       <c r="V89">
-        <v>-26.21979185450551</v>
+        <v>-96.13923679985352</v>
       </c>
       <c r="W89">
-        <v>-41.43571816060101</v>
+        <v>-151.9309665888704</v>
       </c>
       <c r="X89">
-        <v>-64.76006557495293</v>
+        <v>-237.4535737748274</v>
       </c>
       <c r="Y89">
-        <v>-95.01078795294856</v>
+        <v>-348.3728891608114</v>
       </c>
       <c r="Z89">
-        <v>-120.4920067706615</v>
+        <v>-441.8040248257587</v>
       </c>
       <c r="AA89">
-        <v>-134.8827855899173</v>
+        <v>-494.570213829697</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -7988,70 +7988,70 @@
         <v>69</v>
       </c>
       <c r="F90">
-        <v>3.7073918285</v>
+        <v>13.59377003783333</v>
       </c>
       <c r="G90">
-        <v>18.004178865</v>
+        <v>66.015322505</v>
       </c>
       <c r="H90">
-        <v>35.53882558</v>
+        <v>130.3090271266667</v>
       </c>
       <c r="I90">
-        <v>42.3510094222</v>
+        <v>155.2870345480667</v>
       </c>
       <c r="J90">
-        <v>48.648677713</v>
+        <v>178.3784849476666</v>
       </c>
       <c r="K90">
-        <v>62.947113303</v>
+        <v>230.806082111</v>
       </c>
       <c r="L90">
-        <v>69.309386406</v>
+        <v>254.134416822</v>
       </c>
       <c r="M90">
-        <v>84.7170997713</v>
+        <v>310.6293658281</v>
       </c>
       <c r="N90">
-        <v>103.7394607089</v>
+        <v>380.3780225993</v>
       </c>
       <c r="O90">
-        <v>79.55034132616663</v>
+        <v>291.684584862611</v>
       </c>
       <c r="P90">
-        <v>62.3693784664333</v>
+        <v>228.6877210435888</v>
       </c>
       <c r="Q90">
-        <v>55.82930654560868</v>
+        <v>204.7074573338985</v>
       </c>
       <c r="R90">
-        <v>59.33549923812058</v>
+        <v>217.5634972064421</v>
       </c>
       <c r="S90">
-        <v>61.01608165654263</v>
+        <v>223.7256327406563</v>
       </c>
       <c r="T90">
-        <v>65.45691571510717</v>
+        <v>240.008690955393</v>
       </c>
       <c r="U90">
-        <v>67.19615155009836</v>
+        <v>246.3858890170273</v>
       </c>
       <c r="V90">
-        <v>62.88349897522617</v>
+        <v>230.5728295758293</v>
       </c>
       <c r="W90">
-        <v>55.86037525242316</v>
+        <v>204.8213759255516</v>
       </c>
       <c r="X90">
-        <v>47.47571031016815</v>
+        <v>174.0776044706165</v>
       </c>
       <c r="Y90">
-        <v>38.5318812992957</v>
+        <v>141.2835647640842</v>
       </c>
       <c r="Z90">
-        <v>30.45342046349376</v>
+        <v>111.6625416994771</v>
       </c>
       <c r="AA90">
-        <v>22.91724018983757</v>
+        <v>84.02988069607109</v>
       </c>
     </row>
     <row r="91" spans="1:27">
@@ -8071,70 +8071,70 @@
         <v>69</v>
       </c>
       <c r="F91">
-        <v>299.24237394</v>
+        <v>1097.22203778</v>
       </c>
       <c r="G91">
-        <v>689.9881405</v>
+        <v>2529.956515166667</v>
       </c>
       <c r="H91">
-        <v>470.079781736</v>
+        <v>1723.625866365333</v>
       </c>
       <c r="I91">
-        <v>486.430444919</v>
+        <v>1783.578298036334</v>
       </c>
       <c r="J91">
-        <v>489.98965414</v>
+        <v>1796.628731846667</v>
       </c>
       <c r="K91">
-        <v>546.263885011</v>
+        <v>2002.967578373667</v>
       </c>
       <c r="L91">
-        <v>588.7277551761</v>
+        <v>2158.6684356457</v>
       </c>
       <c r="M91">
-        <v>588.4122547203</v>
+        <v>2157.5116006411</v>
       </c>
       <c r="N91">
-        <v>591.6226627709</v>
+        <v>2169.283096826633</v>
       </c>
       <c r="O91">
-        <v>221.05940052086</v>
+        <v>810.5511352431535</v>
       </c>
       <c r="P91">
-        <v>118.0496459678307</v>
+        <v>432.8487018820458</v>
       </c>
       <c r="Q91">
-        <v>63.09758800163742</v>
+        <v>231.3578226726705</v>
       </c>
       <c r="R91">
-        <v>10.4007085223732</v>
+        <v>38.13593124870173</v>
       </c>
       <c r="S91">
-        <v>-31.28270350576203</v>
+        <v>-114.7032461877941</v>
       </c>
       <c r="T91">
-        <v>-57.92751067387742</v>
+        <v>-212.4008724708839</v>
       </c>
       <c r="U91">
-        <v>-71.46063805533269</v>
+        <v>-262.0223395362199</v>
       </c>
       <c r="V91">
-        <v>-81.86958062487402</v>
+        <v>-300.1884622912048</v>
       </c>
       <c r="W91">
-        <v>-98.71386174142852</v>
+        <v>-361.9508263852379</v>
       </c>
       <c r="X91">
-        <v>-122.9068829896943</v>
+        <v>-450.6585709622124</v>
       </c>
       <c r="Y91">
-        <v>-139.3538218372281</v>
+        <v>-510.9640134031695</v>
       </c>
       <c r="Z91">
-        <v>-150.3907985642646</v>
+        <v>-551.4329280689702</v>
       </c>
       <c r="AA91">
-        <v>-161.8089985009538</v>
+        <v>-593.2996611701639</v>
       </c>
     </row>
     <row r="92" spans="1:27">
@@ -8154,70 +8154,70 @@
         <v>69</v>
       </c>
       <c r="F92">
-        <v>30.6799432</v>
+        <v>112.4931250666667</v>
       </c>
       <c r="G92">
-        <v>111.091547888352</v>
+        <v>407.335675590624</v>
       </c>
       <c r="H92">
-        <v>136.320796525</v>
+        <v>499.8429205916667</v>
       </c>
       <c r="I92">
-        <v>143.7346250946</v>
+        <v>527.0269586802</v>
       </c>
       <c r="J92">
-        <v>141.7703061473</v>
+        <v>519.8244558734333</v>
       </c>
       <c r="K92">
-        <v>128.87830533255</v>
+        <v>472.5537862193499</v>
       </c>
       <c r="L92">
-        <v>124.81825569464</v>
+        <v>457.6669375470133</v>
       </c>
       <c r="M92">
-        <v>123.2956551051223</v>
+        <v>452.0840687187818</v>
       </c>
       <c r="N92">
-        <v>122.6985872387188</v>
+        <v>449.8948198753023</v>
       </c>
       <c r="O92">
-        <v>53.198100778235</v>
+        <v>195.0597028535284</v>
       </c>
       <c r="P92">
-        <v>34.13689257039486</v>
+        <v>125.1686060914478</v>
       </c>
       <c r="Q92">
-        <v>26.75515706548108</v>
+        <v>98.10224257343062</v>
       </c>
       <c r="R92">
-        <v>24.8418181213399</v>
+        <v>91.08666644491296</v>
       </c>
       <c r="S92">
-        <v>22.57971314816973</v>
+        <v>82.79228154328901</v>
       </c>
       <c r="T92">
-        <v>19.98122330826799</v>
+        <v>73.26448546364928</v>
       </c>
       <c r="U92">
-        <v>16.99423996357886</v>
+        <v>62.31221319978914</v>
       </c>
       <c r="V92">
-        <v>14.33148736304582</v>
+        <v>52.54878699783468</v>
       </c>
       <c r="W92">
-        <v>11.51500259494315</v>
+        <v>42.22167618145821</v>
       </c>
       <c r="X92">
-        <v>8.966024557977708</v>
+        <v>32.87542337925159</v>
       </c>
       <c r="Y92">
-        <v>8.609674361448615</v>
+        <v>31.56880599197826</v>
       </c>
       <c r="Z92">
-        <v>6.520494553013124</v>
+        <v>23.90848002771479</v>
       </c>
       <c r="AA92">
-        <v>5.023093134307652</v>
+        <v>18.41800815912806</v>
       </c>
     </row>
     <row r="93" spans="1:27">
@@ -8237,70 +8237,70 @@
         <v>69</v>
       </c>
       <c r="F93">
-        <v>10.4999246633</v>
+        <v>38.49972376543334</v>
       </c>
       <c r="G93">
-        <v>30.526308404537</v>
+        <v>111.9297974833024</v>
       </c>
       <c r="H93">
-        <v>48.447463061338</v>
+        <v>177.6406978915727</v>
       </c>
       <c r="I93">
-        <v>53.48845419328</v>
+        <v>196.1243320420267</v>
       </c>
       <c r="J93">
-        <v>52.081331997129</v>
+        <v>190.964883989473</v>
       </c>
       <c r="K93">
-        <v>18.8934201023796</v>
+        <v>69.2758737087252</v>
       </c>
       <c r="L93">
-        <v>21.5899657802328</v>
+        <v>79.1632078608536</v>
       </c>
       <c r="M93">
-        <v>28.305324993938</v>
+        <v>103.7861916444393</v>
       </c>
       <c r="N93">
-        <v>37.7309884864162</v>
+        <v>138.3469577835261</v>
       </c>
       <c r="O93">
-        <v>20.3871822015429</v>
+        <v>74.7530014056573</v>
       </c>
       <c r="P93">
-        <v>14.2321235675455</v>
+        <v>52.18445308100016</v>
       </c>
       <c r="Q93">
-        <v>10.43812405516996</v>
+        <v>38.2731215356232</v>
       </c>
       <c r="R93">
-        <v>7.387198381277328</v>
+        <v>27.08639406468354</v>
       </c>
       <c r="S93">
-        <v>4.004673089037043</v>
+        <v>14.68380132646916</v>
       </c>
       <c r="T93">
-        <v>0.6984613404522624</v>
+        <v>2.561024914991629</v>
       </c>
       <c r="U93">
-        <v>-2.702780629914919</v>
+        <v>-9.910195643021369</v>
       </c>
       <c r="V93">
-        <v>-6.305562996868397</v>
+        <v>-23.12039765518412</v>
       </c>
       <c r="W93">
-        <v>-9.506563744148568</v>
+        <v>-34.85740039521142</v>
       </c>
       <c r="X93">
-        <v>-14.41168033905547</v>
+        <v>-52.84282790987007</v>
       </c>
       <c r="Y93">
-        <v>-21.89364108149178</v>
+        <v>-80.27668396546987</v>
       </c>
       <c r="Z93">
-        <v>-28.73623438937905</v>
+        <v>-105.3661927610565</v>
       </c>
       <c r="AA93">
-        <v>-37.08049227745099</v>
+        <v>-135.9618050173203</v>
       </c>
     </row>
     <row r="94" spans="1:27">
@@ -8320,70 +8320,70 @@
         <v>69</v>
       </c>
       <c r="F94">
-        <v>11.14068783</v>
+        <v>40.84918871</v>
       </c>
       <c r="G94">
-        <v>24.094670319</v>
+        <v>88.34712450299999</v>
       </c>
       <c r="H94">
-        <v>40.8691796131</v>
+        <v>149.8536585813667</v>
       </c>
       <c r="I94">
-        <v>54.105418385</v>
+        <v>198.3865340783333</v>
       </c>
       <c r="J94">
-        <v>61.425480548</v>
+        <v>225.2267620093334</v>
       </c>
       <c r="K94">
-        <v>63.562396851</v>
+        <v>233.062121787</v>
       </c>
       <c r="L94">
-        <v>67.67987878785</v>
+        <v>248.15955555545</v>
       </c>
       <c r="M94">
-        <v>69.28031488633999</v>
+        <v>254.0278212499133</v>
       </c>
       <c r="N94">
-        <v>71.97786793941999</v>
+        <v>263.9188491112066</v>
       </c>
       <c r="O94">
-        <v>31.0126997726025</v>
+        <v>113.7132324995425</v>
       </c>
       <c r="P94">
-        <v>11.5901459219118</v>
+        <v>42.49720171367661</v>
       </c>
       <c r="Q94">
-        <v>-4.57330054923735</v>
+        <v>-16.76876868053695</v>
       </c>
       <c r="R94">
-        <v>-19.7475301794545</v>
+        <v>-72.40761065799985</v>
       </c>
       <c r="S94">
-        <v>-33.80818491615519</v>
+        <v>-123.963344692569</v>
       </c>
       <c r="T94">
-        <v>-45.25941250677859</v>
+        <v>-165.9511791915215</v>
       </c>
       <c r="U94">
-        <v>-57.9293703333792</v>
+        <v>-212.4076912223904</v>
       </c>
       <c r="V94">
-        <v>-72.1718027102698</v>
+        <v>-264.6299432709893</v>
       </c>
       <c r="W94">
-        <v>-88.51431772137333</v>
+        <v>-324.5524983117022</v>
       </c>
       <c r="X94">
-        <v>-111.539023448266</v>
+        <v>-408.9764193103088</v>
       </c>
       <c r="Y94">
-        <v>-137.0754457639094</v>
+        <v>-502.6099678010012</v>
       </c>
       <c r="Z94">
-        <v>-163.7003415666787</v>
+        <v>-600.2345857444888</v>
       </c>
       <c r="AA94">
-        <v>-190.2673069267766</v>
+        <v>-697.6467920648475</v>
       </c>
     </row>
     <row r="95" spans="1:27">
@@ -8403,70 +8403,70 @@
         <v>69</v>
       </c>
       <c r="F95">
-        <v>3.1148930041</v>
+        <v>11.42127434836667</v>
       </c>
       <c r="G95">
-        <v>7.62235648322</v>
+        <v>27.94864043847333</v>
       </c>
       <c r="H95">
-        <v>19.00970764024</v>
+        <v>69.70226134754667</v>
       </c>
       <c r="I95">
-        <v>25.2807926606</v>
+        <v>92.69623975553333</v>
       </c>
       <c r="J95">
-        <v>34.86366746</v>
+        <v>127.8334473533333</v>
       </c>
       <c r="K95">
-        <v>46.036315605</v>
+        <v>168.799823885</v>
       </c>
       <c r="L95">
-        <v>50.34600700032</v>
+        <v>184.60202566784</v>
       </c>
       <c r="M95">
-        <v>61.30501390622</v>
+        <v>224.7850509894733</v>
       </c>
       <c r="N95">
-        <v>73.51887703328001</v>
+        <v>269.5692157886934</v>
       </c>
       <c r="O95">
-        <v>47.58898015631059</v>
+        <v>174.4929272398055</v>
       </c>
       <c r="P95">
-        <v>37.12948094582137</v>
+        <v>136.1414301346784</v>
       </c>
       <c r="Q95">
-        <v>30.10716165665923</v>
+        <v>110.3929260744172</v>
       </c>
       <c r="R95">
-        <v>28.19239768043192</v>
+        <v>103.3721248282504</v>
       </c>
       <c r="S95">
-        <v>27.76608619793173</v>
+        <v>101.8089827257497</v>
       </c>
       <c r="T95">
-        <v>27.01833101246332</v>
+        <v>99.06721371236551</v>
       </c>
       <c r="U95">
-        <v>25.25662918107847</v>
+        <v>92.60764033062105</v>
       </c>
       <c r="V95">
-        <v>22.91328020455089</v>
+        <v>84.01536075001992</v>
       </c>
       <c r="W95">
-        <v>21.94023279152456</v>
+        <v>80.44752023559006</v>
       </c>
       <c r="X95">
-        <v>18.29405714453439</v>
+        <v>67.07820952995942</v>
       </c>
       <c r="Y95">
-        <v>14.27820564335437</v>
+        <v>52.35342069229936</v>
       </c>
       <c r="Z95">
-        <v>10.63788876761847</v>
+        <v>39.0055921479344</v>
       </c>
       <c r="AA95">
-        <v>7.519061029555161</v>
+        <v>27.56989044170226</v>
       </c>
     </row>
     <row r="96" spans="1:27">
@@ -8486,70 +8486,70 @@
         <v>69</v>
       </c>
       <c r="F96">
-        <v>10.67685026</v>
+        <v>39.14845095333333</v>
       </c>
       <c r="G96">
-        <v>76.444830001452</v>
+        <v>280.297710005324</v>
       </c>
       <c r="H96">
-        <v>144.7140606732</v>
+        <v>530.6182224684001</v>
       </c>
       <c r="I96">
-        <v>169.81910517803</v>
+        <v>622.6700523194432</v>
       </c>
       <c r="J96">
-        <v>182.233588030905</v>
+        <v>668.189822779985</v>
       </c>
       <c r="K96">
-        <v>175.684081942998</v>
+        <v>644.174967124326</v>
       </c>
       <c r="L96">
-        <v>177.4392963020035</v>
+        <v>650.6107531073461</v>
       </c>
       <c r="M96">
-        <v>174.7776867406871</v>
+        <v>640.851518049186</v>
       </c>
       <c r="N96">
-        <v>171.0847761804603</v>
+        <v>627.3108459950209</v>
       </c>
       <c r="O96">
-        <v>119.433330030011</v>
+        <v>437.9222101100404</v>
       </c>
       <c r="P96">
-        <v>87.55819695017188</v>
+        <v>321.0467221506302</v>
       </c>
       <c r="Q96">
-        <v>69.87164141676296</v>
+        <v>256.1960185281308</v>
       </c>
       <c r="R96">
-        <v>59.2295397426653</v>
+        <v>217.1749790564395</v>
       </c>
       <c r="S96">
-        <v>50.43836858618496</v>
+        <v>184.9406848160115</v>
       </c>
       <c r="T96">
-        <v>42.9533016117083</v>
+        <v>157.4954392429304</v>
       </c>
       <c r="U96">
-        <v>35.70936828952965</v>
+        <v>130.934350394942</v>
       </c>
       <c r="V96">
-        <v>30.38877642911908</v>
+        <v>111.4255135734366</v>
       </c>
       <c r="W96">
-        <v>26.33642613817894</v>
+        <v>96.56689583998944</v>
       </c>
       <c r="X96">
-        <v>22.87811682134046</v>
+        <v>83.88642834491502</v>
       </c>
       <c r="Y96">
-        <v>20.02094164729559</v>
+        <v>73.41011937341716</v>
       </c>
       <c r="Z96">
-        <v>17.74225544600758</v>
+        <v>65.05493663536113</v>
       </c>
       <c r="AA96">
-        <v>15.8732688469519</v>
+        <v>58.20198577215695</v>
       </c>
     </row>
     <row r="97" spans="1:27">
@@ -8569,70 +8569,70 @@
         <v>69</v>
       </c>
       <c r="F97">
-        <v>36.76990316</v>
+        <v>134.8229782533333</v>
       </c>
       <c r="G97">
-        <v>120.822000304375</v>
+        <v>443.0140011160417</v>
       </c>
       <c r="H97">
-        <v>233.0029986110314</v>
+        <v>854.3443282404487</v>
       </c>
       <c r="I97">
-        <v>286.3061332203409</v>
+        <v>1049.78915514125</v>
       </c>
       <c r="J97">
-        <v>328.1676309439272</v>
+        <v>1203.281313461066</v>
       </c>
       <c r="K97">
-        <v>384.7846333041183</v>
+        <v>1410.876988781767</v>
       </c>
       <c r="L97">
-        <v>409.1349515082217</v>
+        <v>1500.16148886348</v>
       </c>
       <c r="M97">
-        <v>444.998469243266</v>
+        <v>1631.661053891976</v>
       </c>
       <c r="N97">
-        <v>476.494657841313</v>
+        <v>1747.147078751481</v>
       </c>
       <c r="O97">
-        <v>233.9390054773612</v>
+        <v>857.7763534169912</v>
       </c>
       <c r="P97">
-        <v>125.5760832127253</v>
+        <v>460.4456384466596</v>
       </c>
       <c r="Q97">
-        <v>48.58843980759231</v>
+        <v>178.1576126278385</v>
       </c>
       <c r="R97">
-        <v>-10.985753066195</v>
+        <v>-40.28109457604831</v>
       </c>
       <c r="S97">
-        <v>-54.45420499396563</v>
+        <v>-199.6654183112073</v>
       </c>
       <c r="T97">
-        <v>-83.69602777485095</v>
+        <v>-306.8854351744534</v>
       </c>
       <c r="U97">
-        <v>-104.4499353183856</v>
+        <v>-382.983096167414</v>
       </c>
       <c r="V97">
-        <v>-113.7620539511867</v>
+        <v>-417.1275311543513</v>
       </c>
       <c r="W97">
-        <v>-115.2500558791728</v>
+        <v>-422.5835382236335</v>
       </c>
       <c r="X97">
-        <v>-116.7273793244488</v>
+        <v>-428.0003908563124</v>
       </c>
       <c r="Y97">
-        <v>-118.3018463842557</v>
+        <v>-433.773436742271</v>
       </c>
       <c r="Z97">
-        <v>-122.0129157750319</v>
+        <v>-447.380691175117</v>
       </c>
       <c r="AA97">
-        <v>-121.319970970934</v>
+        <v>-444.8398935600915</v>
       </c>
     </row>
     <row r="98" spans="1:27">
@@ -8652,70 +8652,70 @@
         <v>69</v>
       </c>
       <c r="F98">
-        <v>6.7345662939</v>
+        <v>24.6934097443</v>
       </c>
       <c r="G98">
-        <v>35.3351190809</v>
+        <v>129.5621032966334</v>
       </c>
       <c r="H98">
-        <v>78.66162216849</v>
+        <v>288.42594795113</v>
       </c>
       <c r="I98">
-        <v>77.92614730137001</v>
+        <v>285.72920677169</v>
       </c>
       <c r="J98">
-        <v>80.559486531576</v>
+        <v>295.384783949112</v>
       </c>
       <c r="K98">
-        <v>81.177959502977</v>
+        <v>297.6525181775824</v>
       </c>
       <c r="L98">
-        <v>77.127423409904</v>
+        <v>282.8005525029814</v>
       </c>
       <c r="M98">
-        <v>75.35397825878937</v>
+        <v>276.2979202822277</v>
       </c>
       <c r="N98">
-        <v>71.92005158032907</v>
+        <v>263.7068557945399</v>
       </c>
       <c r="O98">
-        <v>49.7268908528239</v>
+        <v>182.331933127021</v>
       </c>
       <c r="P98">
-        <v>32.13876062846828</v>
+        <v>117.8421223043837</v>
       </c>
       <c r="Q98">
-        <v>23.57468646237333</v>
+        <v>86.44051702870222</v>
       </c>
       <c r="R98">
-        <v>18.98797937410516</v>
+        <v>69.62259103838556</v>
       </c>
       <c r="S98">
-        <v>14.75799623722541</v>
+        <v>54.11265286982651</v>
       </c>
       <c r="T98">
-        <v>11.170583941565</v>
+        <v>40.95880778573835</v>
       </c>
       <c r="U98">
-        <v>7.992970153967071</v>
+        <v>29.30755723121259</v>
       </c>
       <c r="V98">
-        <v>5.555553944609983</v>
+        <v>20.37036446356994</v>
       </c>
       <c r="W98">
-        <v>3.405485176147516</v>
+        <v>12.48677897920756</v>
       </c>
       <c r="X98">
-        <v>0.692989882837999</v>
+        <v>2.54096290373933</v>
       </c>
       <c r="Y98">
-        <v>-1.905554059350958</v>
+        <v>-6.987031550953511</v>
       </c>
       <c r="Z98">
-        <v>-3.696349115467541</v>
+        <v>-13.55328009004765</v>
       </c>
       <c r="AA98">
-        <v>-4.767550614521398</v>
+        <v>-17.48101891991179</v>
       </c>
     </row>
     <row r="99" spans="1:27">
@@ -8735,70 +8735,70 @@
         <v>69</v>
       </c>
       <c r="F99">
-        <v>516.9936186</v>
+        <v>1895.6432682</v>
       </c>
       <c r="G99">
-        <v>1400.6891308</v>
+        <v>5135.860146266667</v>
       </c>
       <c r="H99">
-        <v>1638.91332928</v>
+        <v>6009.348874026667</v>
       </c>
       <c r="I99">
-        <v>1529.410123</v>
+        <v>5607.837117666667</v>
       </c>
       <c r="J99">
-        <v>1438.06798541</v>
+        <v>5272.915946503333</v>
       </c>
       <c r="K99">
-        <v>1332.99193917</v>
+        <v>4887.63711029</v>
       </c>
       <c r="L99">
-        <v>1292.0998880832</v>
+        <v>4737.699589638401</v>
       </c>
       <c r="M99">
-        <v>1265.5225853502</v>
+        <v>4640.2494796174</v>
       </c>
       <c r="N99">
-        <v>1226.6668507922</v>
+        <v>4497.778452904733</v>
       </c>
       <c r="O99">
-        <v>722.5466785196001</v>
+        <v>2649.337821238534</v>
       </c>
       <c r="P99">
-        <v>430.0603145843</v>
+        <v>1576.887820142433</v>
       </c>
       <c r="Q99">
-        <v>197.5936252463459</v>
+        <v>724.5099592366014</v>
       </c>
       <c r="R99">
-        <v>30.6325646079124</v>
+        <v>112.3194035623455</v>
       </c>
       <c r="S99">
-        <v>-114.8277093649022</v>
+        <v>-421.0349343379748</v>
       </c>
       <c r="T99">
-        <v>-223.2442680569352</v>
+        <v>-818.5623162087626</v>
       </c>
       <c r="U99">
-        <v>-333.28120980281</v>
+        <v>-1222.031102610303</v>
       </c>
       <c r="V99">
-        <v>-429.0130690527428</v>
+        <v>-1573.047919860057</v>
       </c>
       <c r="W99">
-        <v>-528.0705096888206</v>
+        <v>-1936.258535525675</v>
       </c>
       <c r="X99">
-        <v>-651.2764043280414</v>
+        <v>-2388.013482536152</v>
       </c>
       <c r="Y99">
-        <v>-766.5994770976006</v>
+        <v>-2810.864749357869</v>
       </c>
       <c r="Z99">
-        <v>-844.3037622498205</v>
+        <v>-3095.780461582675</v>
       </c>
       <c r="AA99">
-        <v>-926.8221247838544</v>
+        <v>-3398.347790874133</v>
       </c>
     </row>
     <row r="100" spans="1:27">
@@ -8818,70 +8818,70 @@
         <v>69</v>
       </c>
       <c r="F100">
-        <v>91.95284384</v>
+        <v>337.1604274133334</v>
       </c>
       <c r="G100">
-        <v>210.80527056</v>
+        <v>772.9526587199999</v>
       </c>
       <c r="H100">
-        <v>100.781637089</v>
+        <v>369.5326693263333</v>
       </c>
       <c r="I100">
-        <v>87.12979062078</v>
+        <v>319.47589894286</v>
       </c>
       <c r="J100">
-        <v>62.31136040854</v>
+        <v>228.4749881646467</v>
       </c>
       <c r="K100">
-        <v>52.30090783331</v>
+        <v>191.7699953888033</v>
       </c>
       <c r="L100">
-        <v>50.38967054566</v>
+        <v>184.7621253340867</v>
       </c>
       <c r="M100">
-        <v>54.28903742533</v>
+        <v>199.0598038928767</v>
       </c>
       <c r="N100">
-        <v>58.06529480089</v>
+        <v>212.9060809365967</v>
       </c>
       <c r="O100">
-        <v>28.095540736981</v>
+        <v>103.0169827022637</v>
       </c>
       <c r="P100">
-        <v>17.247189228069</v>
+        <v>63.23969383625299</v>
       </c>
       <c r="Q100">
-        <v>11.05981576962534</v>
+        <v>40.55265782195958</v>
       </c>
       <c r="R100">
-        <v>7.75222049673956</v>
+        <v>28.42480848804506</v>
       </c>
       <c r="S100">
-        <v>5.313555273422687</v>
+        <v>19.48303600254985</v>
       </c>
       <c r="T100">
-        <v>3.887262791733732</v>
+        <v>14.25329690302368</v>
       </c>
       <c r="U100">
-        <v>3.611046206949093</v>
+        <v>13.24050275881334</v>
       </c>
       <c r="V100">
-        <v>3.773915802552625</v>
+        <v>13.83769127602629</v>
       </c>
       <c r="W100">
-        <v>3.721605635769954</v>
+        <v>13.6458873311565</v>
       </c>
       <c r="X100">
-        <v>3.20413311143767</v>
+        <v>11.74848807527146</v>
       </c>
       <c r="Y100">
-        <v>2.387762702658748</v>
+        <v>8.755129909748742</v>
       </c>
       <c r="Z100">
-        <v>1.38228276689191</v>
+        <v>5.068370145270337</v>
       </c>
       <c r="AA100">
-        <v>0.3580857297832861</v>
+        <v>1.312981009205382</v>
       </c>
     </row>
     <row r="101" spans="1:27">
@@ -8901,70 +8901,70 @@
         <v>69</v>
       </c>
       <c r="F101">
-        <v>2380.523956178104</v>
+        <v>8728.587839319713</v>
       </c>
       <c r="G101">
-        <v>6201.846850010113</v>
+        <v>22740.10511670375</v>
       </c>
       <c r="H101">
-        <v>8196.469731564328</v>
+        <v>30053.7223490692</v>
       </c>
       <c r="I101">
-        <v>9310.694019157982</v>
+        <v>34139.21140357927</v>
       </c>
       <c r="J101">
-        <v>9934.615954610279</v>
+        <v>36426.92516690436</v>
       </c>
       <c r="K101">
-        <v>10272.83692404719</v>
+        <v>37667.06872150637</v>
       </c>
       <c r="L101">
-        <v>10947.33920047185</v>
+        <v>40140.24373506344</v>
       </c>
       <c r="M101">
-        <v>11216.91448693623</v>
+        <v>41128.68645209951</v>
       </c>
       <c r="N101">
-        <v>11443.53452819194</v>
+        <v>41959.62660337044</v>
       </c>
       <c r="O101">
-        <v>5779.364027751162</v>
+        <v>21191.00143508759</v>
       </c>
       <c r="P101">
-        <v>3409.949954611135</v>
+        <v>12503.14983357416</v>
       </c>
       <c r="Q101">
-        <v>1959.689939098703</v>
+        <v>7185.529776695243</v>
       </c>
       <c r="R101">
-        <v>1021.566198474898</v>
+        <v>3745.742727741293</v>
       </c>
       <c r="S101">
-        <v>300.2387368179965</v>
+        <v>1100.875368332654</v>
       </c>
       <c r="T101">
-        <v>-239.8452457330159</v>
+        <v>-879.4325676877249</v>
       </c>
       <c r="U101">
-        <v>-754.4570125152899</v>
+        <v>-2766.34237922273</v>
       </c>
       <c r="V101">
-        <v>-1147.548096357275</v>
+        <v>-4207.676353310007</v>
       </c>
       <c r="W101">
-        <v>-1516.995926095977</v>
+        <v>-5562.318395685248</v>
       </c>
       <c r="X101">
-        <v>-1915.934696355146</v>
+        <v>-7025.093886635536</v>
       </c>
       <c r="Y101">
-        <v>-2339.757359426527</v>
+        <v>-8579.110317897266</v>
       </c>
       <c r="Z101">
-        <v>-2678.051951125386</v>
+        <v>-9819.523820793082</v>
       </c>
       <c r="AA101">
-        <v>-3080.517565934394</v>
+        <v>-11295.23107509278</v>
       </c>
     </row>
   </sheetData>
